--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57747</v>
+        <v>57773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57773</v>
+        <v>57775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57775</v>
+        <v>57783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57783</v>
+        <v>57784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57784</v>
+        <v>57785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28317-2023 artfynd.xlsx
+++ b/artfynd/A 28317-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129685263</v>
       </c>
       <c r="B2" t="n">
-        <v>57799</v>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
